--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484747_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484747_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.3014</v>
+        <v>9.149100000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1914</v>
+        <v>7.5681</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1101</v>
+        <v>1.581</v>
       </c>
       <c r="G2" t="n">
         <v>5.8478</v>
@@ -610,13 +610,13 @@
         <v>2.8305</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6613</v>
+        <v>0.5089</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6677</v>
+        <v>0.0444</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9936</v>
+        <v>0.4645</v>
       </c>
       <c r="V2" t="n">
         <v>1.8488</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9277</v>
+        <v>5.986</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7843</v>
+        <v>5.5251</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1435</v>
+        <v>0.4609</v>
       </c>
       <c r="G3" t="n">
         <v>1.9513</v>
@@ -688,13 +688,13 @@
         <v>2.0757</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.967</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0458</v>
+        <v>-0.305</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0788</v>
+        <v>0.3963</v>
       </c>
       <c r="V3" t="n">
         <v>1.8678</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.429</v>
+        <v>4.0573</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3146</v>
+        <v>2.0223</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1144</v>
+        <v>2.035</v>
       </c>
       <c r="G4" t="n">
         <v>4.3302</v>
@@ -766,13 +766,13 @@
         <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4762</v>
+        <v>0.1045</v>
       </c>
       <c r="T4" t="n">
-        <v>0.368</v>
+        <v>0.0757</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1082</v>
+        <v>0.0289</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0674</v>
+        <v>3.3739</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6425</v>
+        <v>1.8962</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4248</v>
+        <v>1.4777</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4559</v>
@@ -844,13 +844,13 @@
         <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5896</v>
+        <v>-0.283</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4674</v>
+        <v>-0.2137</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1222</v>
+        <v>-0.0693</v>
       </c>
       <c r="V5" t="n">
         <v>5.3016</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1173</v>
+        <v>2.3916</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4442</v>
+        <v>1.6391</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6731</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>2.0891</v>
@@ -922,13 +922,13 @@
         <v>0.5661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5379</v>
+        <v>-0.2636</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2939</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2439</v>
+        <v>-0.1646</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4729</v>
+        <v>1.5665</v>
       </c>
       <c r="E7" t="n">
-        <v>1.577</v>
+        <v>1.5383</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1041</v>
+        <v>0.0282</v>
       </c>
       <c r="G7" t="n">
         <v>1.6763</v>
@@ -1000,13 +1000,13 @@
         <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0417</v>
+        <v>0.1354</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1147</v>
+        <v>-0.1533</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1564</v>
+        <v>0.2887</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6226</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3315</v>
+        <v>1.2786</v>
       </c>
       <c r="E8" t="n">
         <v>2.0741</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7426</v>
+        <v>-0.7956</v>
       </c>
       <c r="G8" t="n">
         <v>0.1001</v>
@@ -1078,13 +1078,13 @@
         <v>1.887</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5896</v>
+        <v>0.5367</v>
       </c>
       <c r="T8" t="n">
         <v>0.1328</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4568</v>
+        <v>0.4039</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2452</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0061</v>
+        <v>-0.3068</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1481</v>
+        <v>-0.0468</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1542</v>
+        <v>-0.26</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6237</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9194</v>
+        <v>0.6187</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6031</v>
+        <v>0.4082</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3163</v>
+        <v>0.2105</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3018</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9811</v>
+        <v>-0.339</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0672</v>
+        <v>0.4183</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0483</v>
+        <v>-0.7573</v>
       </c>
       <c r="G10" t="n">
         <v>0.9303</v>
@@ -1234,13 +1234,13 @@
         <v>0.5661</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2321</v>
+        <v>-0.59</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5168</v>
+        <v>-0.1657</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7154</v>
+        <v>-0.4244</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3018</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. VALERO MORANT</t>
+          <t>A. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5949</v>
+        <v>-1.5255</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.07149999999999999</v>
+        <v>1.6587</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5234</v>
+        <v>-3.1842</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4377</v>
+        <v>0.1597</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2647</v>
+        <v>1.1168</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.173</v>
+        <v>-0.957</v>
       </c>
       <c r="J11" t="n">
-        <v>0.08450000000000001</v>
+        <v>2.5002</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08450000000000001</v>
+        <v>3.1327</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.6325</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5222</v>
+        <v>-2.3405</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3492</v>
+        <v>-2.016</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.173</v>
+        <v>-0.3245</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4844</v>
+        <v>0.1825</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4855</v>
+        <v>0.102</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0012</v>
+        <v>0.0806</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-1.8678</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. FONT FENOLLAR</t>
+          <t>J. VALERO MORANT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8262</v>
+        <v>-2.0376</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4638</v>
+        <v>-0.4613</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.29</v>
+        <v>-1.5763</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1597</v>
+        <v>-1.4377</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1168</v>
+        <v>-1.2647</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.957</v>
+        <v>-0.173</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5002</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1327</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6325</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3405</v>
+        <v>-1.5222</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.016</v>
+        <v>-1.3492</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3245</v>
+        <v>-0.173</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1182</v>
+        <v>0.0417</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0929</v>
+        <v>0.0958</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0253</v>
+        <v>-0.0541</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8678</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5327</v>
+        <v>-2.594</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4881</v>
+        <v>-0.3906</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0446</v>
+        <v>-2.2033</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5685</v>
@@ -1468,13 +1468,13 @@
         <v>0.7548</v>
       </c>
       <c r="S13" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2228</v>
+        <v>-0.1254</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3151</v>
+        <v>0.1564</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8678</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>20.7062</v>
+        <v>21.0001</v>
       </c>
       <c r="E14" t="n">
-        <v>23.1476</v>
+        <v>23.44149999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4413</v>
+        <v>-2.4414</v>
       </c>
       <c r="G14" t="n">
         <v>12.999</v>
@@ -1546,16 +1546,16 @@
         <v>14.1525</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8200999999999998</v>
+        <v>1.1141</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4972</v>
+        <v>-0.2033</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3172</v>
+        <v>1.3174</v>
       </c>
       <c r="V14" t="n">
-        <v>2.169600000000001</v>
+        <v>2.1696</v>
       </c>
       <c r="W14" t="n">
         <v>8.9612</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8551</v>
+        <v>1.0843</v>
       </c>
       <c r="E15" t="n">
-        <v>3.039</v>
+        <v>2.7467</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1839</v>
+        <v>-1.6625</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1124</v>
@@ -1624,13 +1624,13 @@
         <v>1.5096</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5373</v>
+        <v>0.7664</v>
       </c>
       <c r="T15" t="n">
-        <v>0.442</v>
+        <v>0.1497</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0953</v>
+        <v>0.6167</v>
       </c>
       <c r="V15" t="n">
         <v>-0.0793</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CABALLERO ROMERO</t>
+          <t>M. VARELA BARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.009299999999999999</v>
+        <v>-0.3632</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3309</v>
+        <v>3.4832</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3216</v>
+        <v>-3.8464</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.0643</v>
+        <v>2.0142</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5034</v>
+        <v>1.7178</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5609</v>
+        <v>0.2964</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.8019</v>
+        <v>3.7935</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5439000000000001</v>
+        <v>4.3849</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.258</v>
+        <v>-0.5914</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2624</v>
+        <v>-1.7792</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9595</v>
+        <v>-2.6671</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.303</v>
+        <v>0.8878</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3774</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3774</v>
+        <v>1.1322</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8094</v>
+        <v>-0.3774</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8875999999999999</v>
+        <v>-0.291</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0864</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8868</v>
+        <v>-1.2452</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2452</v>
+        <v>1.8678</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6415999999999999</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>A. CABALLERO ROMERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5003</v>
+        <v>-0.3864</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3451</v>
+        <v>-0.3511</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8454</v>
+        <v>-0.0353</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8774999999999999</v>
+        <v>-3.0643</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0667</v>
+        <v>-1.5034</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9442</v>
+        <v>-1.5609</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1355</v>
+        <v>-1.8019</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8194</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3162</v>
+        <v>-1.258</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.258</v>
+        <v>-1.2624</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.886</v>
+        <v>-0.9595</v>
       </c>
       <c r="O17" t="n">
-        <v>0.628</v>
+        <v>-0.303</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3774</v>
+        <v>0.3774</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5661</v>
+        <v>0.3774</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8864</v>
+        <v>0.4137</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7947</v>
+        <v>0.2056</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0917</v>
+        <v>0.2081</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8868</v>
+        <v>1.8868</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.2452</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2452</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. VARELA BARCIA</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9886</v>
+        <v>-1.1378</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0935</v>
+        <v>0.7605</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.0821</v>
+        <v>-1.8983</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0142</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7178</v>
+        <v>-1.0667</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2964</v>
+        <v>1.9442</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7935</v>
+        <v>2.1355</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3849</v>
+        <v>0.8194</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5914</v>
+        <v>1.3162</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7792</v>
+        <v>-1.258</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.6671</v>
+        <v>-1.886</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8878</v>
+        <v>0.628</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7548</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1322</v>
+        <v>0.5661</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0029</v>
+        <v>0.2489</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6808</v>
+        <v>0.2101</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3221</v>
+        <v>0.0388</v>
       </c>
       <c r="V18" t="n">
+        <v>-1.8868</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.6415999999999999</v>
+      </c>
+      <c r="X18" t="n">
         <v>-1.2452</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.8678</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-3.113</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0687</v>
+        <v>-1.8167</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1821</v>
+        <v>0.5975</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2507</v>
+        <v>-2.4142</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6051</v>
@@ -1936,13 +1936,13 @@
         <v>1.6983</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7101</v>
+        <v>0.962</v>
       </c>
       <c r="T19" t="n">
-        <v>0.974</v>
+        <v>0.3894</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7361</v>
+        <v>0.5726</v>
       </c>
       <c r="V19" t="n">
         <v>-0.0414</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. ZOROA GARCIA</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2721</v>
+        <v>-1.9176</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3744</v>
+        <v>-0.031</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-1.8866</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0422</v>
+        <v>-0.7396</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4617</v>
+        <v>-0.5705</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5805</v>
+        <v>-0.169</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2569</v>
+        <v>1.5367</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0423</v>
+        <v>1.5112</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2991</v>
+        <v>0.0256</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7854</v>
+        <v>-2.2763</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.504</v>
+        <v>-2.0817</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2814</v>
+        <v>-0.1946</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2299</v>
+        <v>-0.495</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1176</v>
+        <v>-0.3034</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1123</v>
+        <v>-0.1916</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2604</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3622</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>E. ZOROA GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6248</v>
+        <v>-2.1157</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4208</v>
+        <v>-1.3744</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.204</v>
+        <v>-0.7413</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7396</v>
+        <v>-2.0422</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5705</v>
+        <v>-0.4617</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.169</v>
+        <v>-1.5805</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5367</v>
+        <v>-1.2569</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5112</v>
+        <v>0.0423</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0256</v>
+        <v>-1.2991</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2763</v>
+        <v>-0.7854</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0817</v>
+        <v>-0.504</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1946</v>
+        <v>-0.2814</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2022</v>
+        <v>-0.0735</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6931</v>
+        <v>-0.1176</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5091</v>
+        <v>0.0441</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2604</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3622</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7097</v>
+        <v>-2.2345</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3081</v>
+        <v>-1.0158</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4015</v>
+        <v>-1.2187</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2314</v>
@@ -2170,13 +2170,13 @@
         <v>1.1322</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3421</v>
+        <v>0.133</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9994</v>
+        <v>-0.7071</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6573</v>
+        <v>0.8401</v>
       </c>
       <c r="V22" t="n">
         <v>1.5056</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. MOLLERMARK</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7291</v>
+        <v>-2.4094</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8578</v>
+        <v>1.5296</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8713</v>
+        <v>-3.939</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.852</v>
+        <v>-0.6839</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8931</v>
+        <v>-0.8961</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0411</v>
+        <v>0.2122</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1523</v>
+        <v>1.7865</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5439000000000001</v>
+        <v>1.1199</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.6666</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6996</v>
+        <v>-2.4704</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3492</v>
+        <v>-2.016</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6496</v>
+        <v>-0.4544</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0664</v>
+        <v>-0.2352</v>
       </c>
       <c r="T23" t="n">
-        <v>0.238</v>
+        <v>-0.2569</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1716</v>
+        <v>0.0218</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.8678</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>R. MOLLERMARK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9532</v>
+        <v>-2.6942</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1398</v>
+        <v>-1.9552</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.093</v>
+        <v>-0.739</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6839</v>
+        <v>-1.852</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8961</v>
+        <v>-1.8931</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2122</v>
+        <v>0.0411</v>
       </c>
       <c r="J24" t="n">
-        <v>1.7865</v>
+        <v>-1.1523</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1199</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6666</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4704</v>
+        <v>-0.6996</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.016</v>
+        <v>-1.3492</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4544</v>
+        <v>0.6496</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3774</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7789</v>
+        <v>0.1012</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.1406</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1322</v>
+        <v>-0.0394</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.8678</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.7242</v>
+        <v>-5.4157</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7279</v>
+        <v>-1.9484</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.9963</v>
+        <v>-3.4673</v>
       </c>
       <c r="G25" t="n">
         <v>-3.5598</v>
@@ -2404,13 +2404,13 @@
         <v>1.6983</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.2738</v>
+        <v>-0.9653</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5161</v>
+        <v>-0.7367</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7577</v>
+        <v>-0.2286</v>
       </c>
       <c r="V25" t="n">
         <v>-0.7019</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-20.7063</v>
+        <v>-19.4069</v>
       </c>
       <c r="E26" t="n">
-        <v>2.4414</v>
+        <v>2.441600000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-23.1475</v>
+        <v>-21.8486</v>
       </c>
       <c r="G26" t="n">
         <v>-12.999</v>
       </c>
       <c r="H26" t="n">
-        <v>-9.751099999999999</v>
+        <v>-9.751100000000001</v>
       </c>
       <c r="I26" t="n">
         <v>-3.2477</v>
@@ -2461,7 +2461,7 @@
         <v>15.7772</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.6574</v>
+        <v>-4.657400000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-24.1184</v>
@@ -2482,13 +2482,13 @@
         <v>9.435</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8202000000000003</v>
+        <v>0.4787999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.3174</v>
+        <v>-1.3173</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4971999999999999</v>
+        <v>1.7962</v>
       </c>
       <c r="V26" t="n">
         <v>-2.1696</v>
